--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.18137477089782</v>
+        <v>6.204473400270896</v>
       </c>
       <c r="D2" t="n">
-        <v>37.14680734991602</v>
+        <v>6.036356194361354</v>
       </c>
       <c r="E2" t="n">
-        <v>6.561950785648731</v>
+        <v>1.066317002667919</v>
       </c>
       <c r="F2" t="n">
-        <v>6.100295785297533</v>
+        <v>0.9912980651108492</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.05747319960036</v>
+        <v>4.071839394935058</v>
       </c>
       <c r="D3" t="n">
-        <v>24.94621577932096</v>
+        <v>4.053760064139656</v>
       </c>
       <c r="E3" t="n">
-        <v>6.561950785648731</v>
+        <v>1.066317002667919</v>
       </c>
       <c r="F3" t="n">
-        <v>6.100295785297533</v>
+        <v>0.9912980651108492</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
